--- a/data/trans_orig/P37A$medicoedad-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P37A$medicoedad-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>142525</t>
+          <t>139423</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>188348</t>
+          <t>183712</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>254645</t>
+          <t>253294</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>310706</t>
+          <t>313898</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>411866</t>
+          <t>409367</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>485509</t>
+          <t>484980</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59446</t>
+          <t>59189</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92029</t>
+          <t>92446</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50454</t>
+          <t>51324</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82119</t>
+          <t>81958</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117759</t>
+          <t>118925</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>165543</t>
+          <t>165747</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>2170</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12775</t>
+          <t>12889</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8391</t>
+          <t>7529</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4561</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15438</t>
+          <t>15484</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23788</t>
+          <t>23736</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48061</t>
+          <t>46353</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24412</t>
+          <t>24231</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47876</t>
+          <t>48860</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53658</t>
+          <t>53791</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>85970</t>
+          <t>86970</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6067</t>
+          <t>6779</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>956</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8035</t>
+          <t>8089</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11702</t>
+          <t>10832</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8568</t>
+          <t>8184</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7921</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21481</t>
+          <t>22837</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46266</t>
+          <t>46561</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19528</t>
+          <t>19582</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42183</t>
+          <t>42860</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46505</t>
+          <t>47076</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79108</t>
+          <t>79110</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19035</t>
+          <t>18452</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40489</t>
+          <t>38972</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16930</t>
+          <t>16907</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38129</t>
+          <t>37284</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40485</t>
+          <t>40819</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>70204</t>
+          <t>68564</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8386</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25655</t>
+          <t>26489</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15406</t>
+          <t>15373</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15235</t>
+          <t>15226</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35293</t>
+          <t>35913</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23693</t>
+          <t>23033</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48463</t>
+          <t>48407</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23555</t>
+          <t>22818</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47263</t>
+          <t>47925</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50583</t>
+          <t>51552</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85508</t>
+          <t>87023</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>6874</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>975</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7961</t>
+          <t>7960</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10868</t>
+          <t>10462</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>882</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9880</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1995,39 +1995,39 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>881</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
           <t>0,06%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>881</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>5289</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9905</t>
+          <t>11254</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22046</t>
+          <t>22045</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8752</t>
+          <t>9420</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25227</t>
+          <t>25460</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18656</t>
+          <t>19087</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41471</t>
+          <t>41441</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5165</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20124</t>
+          <t>20598</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>802</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>7424</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>7299</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23423</t>
+          <t>23384</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7434</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21575</t>
+          <t>22090</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13311</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12699</t>
+          <t>12556</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>31681</t>
+          <t>30659</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14387</t>
+          <t>14978</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34957</t>
+          <t>34471</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9485</t>
+          <t>10228</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27092</t>
+          <t>27933</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29098</t>
+          <t>28955</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>53913</t>
+          <t>55946</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>904</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>11606</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,82 +2564,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>6189</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>4881</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>13535</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1236</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>6210</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>4881</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>1223</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>12198</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>182065</t>
+          <t>181837</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>233678</t>
+          <t>233155</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>296561</t>
+          <t>294153</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>363853</t>
+          <t>367029</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>494405</t>
+          <t>490841</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>585031</t>
+          <t>585437</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92818</t>
+          <t>93850</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>134187</t>
+          <t>134078</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>76264</t>
+          <t>75676</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>114793</t>
+          <t>112191</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>180170</t>
+          <t>179404</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>236111</t>
+          <t>232890</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24270</t>
+          <t>24584</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>48014</t>
+          <t>48567</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11597</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>28389</t>
+          <t>28172</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>39283</t>
+          <t>39214</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>66045</t>
+          <t>68139</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>74819</t>
+          <t>73364</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>113119</t>
+          <t>111372</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>67545</t>
+          <t>69680</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>108075</t>
+          <t>105793</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>151285</t>
+          <t>152147</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>205842</t>
+          <t>207189</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14457</t>
+          <t>14692</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15080</t>
+          <t>14612</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8652</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>24923</t>
+          <t>25425</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>876</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8415</t>
+          <t>8839</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10156</t>
+          <t>10786</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>15158</t>
+          <t>15682</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>211418</t>
+          <t>209565</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>264739</t>
+          <t>266385</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>286792</t>
+          <t>284334</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>347295</t>
+          <t>350507</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>509530</t>
+          <t>510978</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>596696</t>
+          <t>595794</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,76%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56064</t>
+          <t>55131</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89779</t>
+          <t>89975</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69169</t>
+          <t>70207</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>106755</t>
+          <t>105758</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>133360</t>
+          <t>133832</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>184526</t>
+          <t>182590</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20292</t>
+          <t>21419</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45088</t>
+          <t>44647</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24220</t>
+          <t>24027</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48223</t>
+          <t>46187</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51360</t>
+          <t>50727</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83088</t>
+          <t>83483</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10676</t>
+          <t>11699</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12925</t>
+          <t>13022</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5975</t>
+          <t>5634</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21642</t>
+          <t>20078</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>6722</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47875</t>
+          <t>47762</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80677</t>
+          <t>81270</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34774</t>
+          <t>33415</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64805</t>
+          <t>62686</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>88914</t>
+          <t>89709</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>133317</t>
+          <t>133392</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35478</t>
+          <t>35101</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63867</t>
+          <t>63626</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31212</t>
+          <t>30285</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59785</t>
+          <t>56872</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72974</t>
+          <t>73239</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113535</t>
+          <t>112095</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18016</t>
+          <t>16685</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40977</t>
+          <t>40186</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>11094</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29258</t>
+          <t>29109</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32206</t>
+          <t>31354</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>60807</t>
+          <t>60519</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45003</t>
+          <t>44284</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78082</t>
+          <t>75536</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>18439</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38703</t>
+          <t>40699</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69821</t>
+          <t>69341</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107309</t>
+          <t>106222</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20306</t>
+          <t>19384</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8911</t>
+          <t>8119</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25035</t>
+          <t>24613</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16111</t>
+          <t>15906</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37781</t>
+          <t>37759</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6782</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10507</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>12332</t>
+          <t>12244</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8093</t>
+          <t>8004</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26286</t>
+          <t>25697</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11656</t>
+          <t>11489</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11994</t>
+          <t>13031</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31977</t>
+          <t>32264</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13716</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22790</t>
+          <t>22010</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9497</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28428</t>
+          <t>28615</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9964</t>
+          <t>10786</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28977</t>
+          <t>28833</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23549</t>
+          <t>23079</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20166</t>
+          <t>20568</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>44253</t>
+          <t>46491</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6684</t>
+          <t>6942</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20728</t>
+          <t>21784</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16172</t>
+          <t>15350</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12379</t>
+          <t>11986</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32276</t>
+          <t>32781</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9616</t>
+          <t>11841</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>995</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11665</t>
+          <t>11404</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>15650</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>283304</t>
+          <t>280657</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>348494</t>
+          <t>351348</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>331402</t>
+          <t>328922</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>403426</t>
+          <t>405319</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>633358</t>
+          <t>633702</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>731888</t>
+          <t>738847</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>103312</t>
+          <t>102856</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>149427</t>
+          <t>147739</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>118811</t>
+          <t>119454</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>165828</t>
+          <t>168227</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>239671</t>
+          <t>235396</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>304536</t>
+          <t>300330</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>33950</t>
+          <t>32875</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>64393</t>
+          <t>63554</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21340</t>
+          <t>21177</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>44994</t>
+          <t>47275</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>60235</t>
+          <t>59470</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>98268</t>
+          <t>98105</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>85716</t>
+          <t>85813</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>126795</t>
+          <t>126463</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53873</t>
+          <t>53610</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>88674</t>
+          <t>86513</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>147806</t>
+          <t>149151</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>201830</t>
+          <t>200712</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9946</t>
+          <t>9812</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27683</t>
+          <t>27024</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16982</t>
+          <t>17284</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>39354</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30811</t>
+          <t>29072</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>58261</t>
+          <t>58383</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6638</t>
+          <t>6737</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>12369</t>
+          <t>12038</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>14495</t>
+          <t>14358</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>160675</t>
+          <t>162899</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>205550</t>
+          <t>207582</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>235547</t>
+          <t>233608</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>297578</t>
+          <t>292811</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>413827</t>
+          <t>410533</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>490157</t>
+          <t>483711</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33461</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58975</t>
+          <t>58491</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39227</t>
+          <t>38341</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69918</t>
+          <t>67948</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77852</t>
+          <t>78312</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>117828</t>
+          <t>118529</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13885</t>
+          <t>14752</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31395</t>
+          <t>32351</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16247</t>
+          <t>15453</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37849</t>
+          <t>37228</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35482</t>
+          <t>34731</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63765</t>
+          <t>63239</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>972</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10295</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>13034</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4968</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17619</t>
+          <t>18841</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>967</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8309</t>
+          <t>9136</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81823</t>
+          <t>82970</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>122599</t>
+          <t>122636</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>81484</t>
+          <t>80429</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>124418</t>
+          <t>126220</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>173295</t>
+          <t>175342</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>231790</t>
+          <t>232800</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46440</t>
+          <t>45090</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78458</t>
+          <t>78241</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29806</t>
+          <t>32136</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>58817</t>
+          <t>58866</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>84403</t>
+          <t>84494</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>126017</t>
+          <t>125238</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16982</t>
+          <t>17360</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17354</t>
+          <t>17682</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11083</t>
+          <t>11156</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28933</t>
+          <t>28824</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15533</t>
+          <t>14930</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36248</t>
+          <t>36935</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17274</t>
+          <t>17376</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40209</t>
+          <t>38861</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37499</t>
+          <t>37322</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66883</t>
+          <t>66439</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6400</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22062</t>
+          <t>21142</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5830</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19658</t>
+          <t>19481</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15784</t>
+          <t>15223</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34786</t>
+          <t>36552</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7898,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>12939</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7933,12 +7933,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14575</t>
+          <t>13247</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7948,12 +7948,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7968,12 +7968,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>6346</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>22577</t>
+          <t>20817</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7983,12 +7983,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14873</t>
+          <t>14084</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36082</t>
+          <t>34473</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7078</t>
+          <t>6935</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24827</t>
+          <t>25336</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24747</t>
+          <t>25794</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50239</t>
+          <t>53327</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5924</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21425</t>
+          <t>21533</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6443</t>
+          <t>6951</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20605</t>
+          <t>20611</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15900</t>
+          <t>15531</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35920</t>
+          <t>36622</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11417</t>
+          <t>11657</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>4554</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18734</t>
+          <t>17458</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25050</t>
+          <t>24710</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15152</t>
+          <t>16891</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5563</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19679</t>
+          <t>20405</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12751</t>
+          <t>12949</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30329</t>
+          <t>31775</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>903</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10984</t>
+          <t>12011</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13388</t>
+          <t>13015</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18074</t>
+          <t>18994</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -8580,12 +8580,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1391</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12696</t>
+          <t>13290</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8595,12 +8595,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8615,12 +8615,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>880</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9622</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8635,7 +8635,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8650,12 +8650,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>16912</t>
+          <t>18307</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8665,12 +8665,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>277185</t>
+          <t>274129</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>337935</t>
+          <t>340085</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>340186</t>
+          <t>341031</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>418339</t>
+          <t>421304</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>638802</t>
+          <t>636296</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>738899</t>
+          <t>736310</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>97049</t>
+          <t>97536</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>141536</t>
+          <t>145079</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>87588</t>
+          <t>87287</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>130517</t>
+          <t>128358</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>194222</t>
+          <t>195524</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>252994</t>
+          <t>256551</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>8188</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25458</t>
+          <t>25004</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>11519</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29447</t>
+          <t>29056</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>23402</t>
+          <t>23946</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>48243</t>
+          <t>49313</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>41729</t>
+          <t>40334</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>71409</t>
+          <t>71761</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>48587</t>
+          <t>50723</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>81938</t>
+          <t>83115</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>98494</t>
+          <t>98753</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>143283</t>
+          <t>142588</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12703</t>
+          <t>12776</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>31595</t>
+          <t>32660</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14581</t>
+          <t>14571</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>34871</t>
+          <t>34511</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>31701</t>
+          <t>31490</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>59192</t>
+          <t>58389</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -9262,12 +9262,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>6719</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>22326</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9297,12 +9297,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>5576</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>20045</t>
+          <t>19860</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9317,7 +9317,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9332,12 +9332,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>15616</t>
+          <t>15420</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>36427</t>
+          <t>37771</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9347,12 +9347,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -9605,32 +9605,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>179546</t>
+          <t>190432</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>160338</t>
+          <t>169299</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>198019</t>
+          <t>212499</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9640,32 +9640,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>329907</t>
+          <t>353487</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>308990</t>
+          <t>330673</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>349123</t>
+          <t>375043</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9675,32 +9675,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>509453</t>
+          <t>543918</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>480628</t>
+          <t>515143</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>536178</t>
+          <t>575430</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>41,09%</t>
         </is>
       </c>
     </row>
@@ -9718,32 +9718,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50474</t>
+          <t>54333</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39326</t>
+          <t>43316</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63638</t>
+          <t>69688</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9753,32 +9753,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>88925</t>
+          <t>99848</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75945</t>
+          <t>85618</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>101588</t>
+          <t>113990</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9788,32 +9788,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>139399</t>
+          <t>154181</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>122732</t>
+          <t>136798</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>158401</t>
+          <t>173725</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2329</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7830</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,32 +9866,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8221</t>
+          <t>8794</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9901,32 +9901,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>5648</t>
+          <t>6054</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12788</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38657</t>
+          <t>41967</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30147</t>
+          <t>31888</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52761</t>
+          <t>55475</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>53583</t>
+          <t>59158</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42598</t>
+          <t>48138</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64008</t>
+          <t>70820</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>92240</t>
+          <t>101125</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78485</t>
+          <t>86699</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109567</t>
+          <t>118352</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -10057,67 +10057,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>7601</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2364</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12135</t>
+          <t>14407</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>7376</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>3746</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>12341</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>6179</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>3094</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>10553</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>12279</t>
+          <t>14977</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>9255</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19936</t>
+          <t>23349</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -10170,32 +10170,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>911</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10205,32 +10205,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4819</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8695</t>
+          <t>9348</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10240,32 +10240,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>7945</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4180</t>
+          <t>4208</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14753</t>
+          <t>14515</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -10287,32 +10287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>167968</t>
+          <t>186192</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>117124</t>
+          <t>165191</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>198145</t>
+          <t>208692</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>377207</t>
+          <t>190578</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>182948</t>
+          <t>170473</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>843551</t>
+          <t>210517</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>545175</t>
+          <t>376770</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>339049</t>
+          <t>345785</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1203667</t>
+          <t>406804</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>102590</t>
+          <t>110897</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70646</t>
+          <t>91533</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>125886</t>
+          <t>133610</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>90236</t>
+          <t>99892</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65743</t>
+          <t>84610</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>109919</t>
+          <t>117573</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>192826</t>
+          <t>210790</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>149538</t>
+          <t>185155</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>223281</t>
+          <t>237773</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -10513,102 +10513,102 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>52008</t>
+          <t>54517</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34040</t>
+          <t>40875</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70653</t>
+          <t>70590</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>66009</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>52469</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>81159</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>120526</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>99788</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>141184</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>2,27%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>62952</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>45512</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>79822</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>114960</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>90039</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>141311</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>154692</t>
+          <t>173302</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>108681</t>
+          <t>147146</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>185789</t>
+          <t>201326</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>152132</t>
+          <t>168672</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>113786</t>
+          <t>146921</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>182899</t>
+          <t>192596</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>306824</t>
+          <t>341974</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>245662</t>
+          <t>309269</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>351091</t>
+          <t>379306</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -10739,27 +10739,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10597</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23384</t>
+          <t>22664</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>27329</t>
+          <t>30719</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17592</t>
+          <t>21821</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37458</t>
+          <t>42153</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>37926</t>
+          <t>42012</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25907</t>
+          <t>30924</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52564</t>
+          <t>56874</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -10852,32 +10852,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15618</t>
+          <t>16364</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9172</t>
+          <t>9061</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26636</t>
+          <t>28000</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10887,32 +10887,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21944</t>
+          <t>25393</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13496</t>
+          <t>16260</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>35098</t>
+          <t>37570</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10922,32 +10922,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>37562</t>
+          <t>41757</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>25116</t>
+          <t>30180</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>53448</t>
+          <t>58964</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -10969,32 +10969,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>76771</t>
+          <t>84688</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>63452</t>
+          <t>70101</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92757</t>
+          <t>101389</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11004,32 +11004,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>49732</t>
+          <t>57621</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40696</t>
+          <t>47584</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61839</t>
+          <t>69632</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11039,32 +11039,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>126504</t>
+          <t>142309</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>109564</t>
+          <t>124119</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>144327</t>
+          <t>164378</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>27930</t>
+          <t>31872</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19605</t>
+          <t>22165</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39264</t>
+          <t>43784</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>30301</t>
+          <t>35152</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22972</t>
+          <t>26545</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39613</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>58231</t>
+          <t>67024</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46576</t>
+          <t>53658</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>72124</t>
+          <t>82432</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>35746</t>
+          <t>37982</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25197</t>
+          <t>27541</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50029</t>
+          <t>51246</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,32 +11230,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>44657</t>
+          <t>47647</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33075</t>
+          <t>37284</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>56733</t>
+          <t>63027</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>80402</t>
+          <t>85629</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>63647</t>
+          <t>68787</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>99250</t>
+          <t>102620</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -11308,32 +11308,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>56717</t>
+          <t>59167</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42706</t>
+          <t>45018</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>72932</t>
+          <t>76389</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,32 +11343,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>58631</t>
+          <t>64919</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47164</t>
+          <t>52877</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>70953</t>
+          <t>78672</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>115348</t>
+          <t>124086</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>97594</t>
+          <t>104983</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>135134</t>
+          <t>145725</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -11421,32 +11421,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8932</t>
+          <t>9339</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,32 +11456,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>10292</t>
+          <t>11186</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17440</t>
+          <t>18798</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11491,32 +11491,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>14311</t>
+          <t>15335</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8576</t>
+          <t>9057</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22197</t>
+          <t>23355</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -11534,32 +11534,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11554</t>
+          <t>13279</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>6935</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24465</t>
+          <t>25967</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11569,32 +11569,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>8865</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14304</t>
+          <t>15988</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11604,32 +11604,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>19621</t>
+          <t>22144</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>12709</t>
+          <t>14194</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>33972</t>
+          <t>34189</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -11651,32 +11651,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>424286</t>
+          <t>461312</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>328285</t>
+          <t>427984</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>470012</t>
+          <t>498922</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11686,32 +11686,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>756846</t>
+          <t>601686</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>570412</t>
+          <t>568795</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1300691</t>
+          <t>640427</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11721,32 +11721,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1181132</t>
+          <t>1062997</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>973924</t>
+          <t>1014733</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1817935</t>
+          <t>1109259</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>180994</t>
+          <t>197102</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>142333</t>
+          <t>172028</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>209755</t>
+          <t>227771</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>209462</t>
+          <t>234892</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>167900</t>
+          <t>211098</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>236352</t>
+          <t>258846</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>390456</t>
+          <t>431994</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>333625</t>
+          <t>398492</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>435964</t>
+          <t>468617</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>90082</t>
+          <t>94807</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>67664</t>
+          <t>76225</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>111326</t>
+          <t>116610</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>110929</t>
+          <t>117402</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>89273</t>
+          <t>98433</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>133384</t>
+          <t>137782</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>201011</t>
+          <t>212209</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>170364</t>
+          <t>186413</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>234777</t>
+          <t>241161</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>250066</t>
+          <t>274436</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>199253</t>
+          <t>240985</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>285599</t>
+          <t>309044</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>264346</t>
+          <t>292749</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>220027</t>
+          <t>264642</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>298612</t>
+          <t>321636</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>514412</t>
+          <t>567185</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>445984</t>
+          <t>523338</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>569440</t>
+          <t>610179</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -12103,67 +12103,67 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>20716</t>
+          <t>23043</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13037</t>
+          <t>14454</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>34692</t>
+          <t>34720</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>49281</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>37814</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>61735</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>43800</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>32131</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>56752</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>64516</t>
+          <t>72324</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>51132</t>
+          <t>57661</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>82637</t>
+          <t>90050</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -12216,32 +12216,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>30299</t>
+          <t>32872</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>19177</t>
+          <t>21831</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>45696</t>
+          <t>47772</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12251,32 +12251,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>34830</t>
+          <t>39162</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>28162</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>48035</t>
+          <t>53975</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12286,32 +12286,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>65128</t>
+          <t>72034</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>49356</t>
+          <t>55604</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>84647</t>
+          <t>92587</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P37A$medicoedad-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P37A$medicoedad-Estudios-trans_orig.xlsx
@@ -718,7 +718,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>medicoedad</t>
+          <t>El médico, por la edad</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -831,7 +831,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>medicoenfermedad</t>
+          <t>El médico, por enfermedades</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -944,112 +944,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>vacunaempresa</t>
+          <t>El médico, por otras razones</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5850</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2170</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12889</t>
+          <t>6779</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>3004</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>956</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>8089</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>4901</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>1901</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>10832</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2821</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>897</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>7529</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>8671</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>3915</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>15484</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -1057,112 +1057,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>vacunapreferencia</t>
+          <t>Otras personas</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33952</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23736</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46353</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35105</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24231</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48860</t>
+          <t>8184</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>69056</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53791</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86970</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -1170,112 +1170,112 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>medicootras</t>
+          <t>La empresa/centro de estudios</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>5850</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2170</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6779</t>
+          <t>12889</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2821</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>7529</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>8671</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>3915</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>15484</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>0,66%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>3004</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>956</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>8089</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>4901</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1901</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>10832</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -1283,112 +1283,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>otros</t>
+          <t>Por voluntad propia</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33952</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23736</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46353</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>35105</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24231</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8184</t>
+          <t>48860</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>67</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>69056</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53791</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>86970</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>medicoedad</t>
+          <t>El médico, por la edad</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>medicoenfermedad</t>
+          <t>El médico, por enfermedades</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1626,112 +1626,112 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>vacunaempresa</t>
+          <t>El médico, por otras razones</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15705</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9167</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26489</t>
+          <t>6874</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8148</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>975</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15373</t>
+          <t>7960</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>23853</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15226</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35913</t>
+          <t>10462</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -1739,112 +1739,112 @@
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>vacunapreferencia</t>
+          <t>Otras personas</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>33565</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23033</t>
+          <t>882</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48407</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33382</t>
+          <t>881</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22818</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47925</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>66947</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51552</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>87023</t>
+          <t>11254</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -1852,112 +1852,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>medicootras</t>
+          <t>La empresa/centro de estudios</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>15705</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>26489</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>8148</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7960</t>
+          <t>15373</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>23853</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>15226</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10462</t>
+          <t>35913</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -1965,112 +1965,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>otros</t>
+          <t>Por voluntad propia</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>33565</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>23033</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>48407</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>33382</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22818</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>47925</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>61</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t>66947</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>51552</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11254</t>
+          <t>87023</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>medicoedad</t>
+          <t>El médico, por la edad</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>medicoenfermedad</t>
+          <t>El médico, por enfermedades</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2308,112 +2308,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>vacunaempresa</t>
+          <t>El médico, por otras razones</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13299</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7460</t>
+          <t>904</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22090</t>
+          <t>11606</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6917</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>20216</t>
+          <t>4881</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12556</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30659</t>
+          <t>13535</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -2421,112 +2421,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>vacunapreferencia</t>
+          <t>Otras personas</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23283</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14978</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34471</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17335</t>
+          <t>981</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10228</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27933</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>40619</t>
+          <t>981</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28955</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55946</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -2534,112 +2534,112 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>medicootras</t>
+          <t>La empresa/centro de estudios</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3646</t>
+          <t>13299</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>22090</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>6917</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>4881</t>
+          <t>20216</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>12556</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13535</t>
+          <t>30659</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -2647,112 +2647,112 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>otros</t>
+          <t>Por voluntad propia</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23283</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14978</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34471</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>17335</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10228</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5946</t>
+          <t>27933</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>39</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>40619</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28955</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>55946</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>medicoedad</t>
+          <t>El médico, por la edad</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>medicoenfermedad</t>
+          <t>El médico, por enfermedades</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2990,112 +2990,112 @@
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>vacunaempresa</t>
+          <t>El médico, por otras razones</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>34855</t>
+          <t>7384</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24584</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>48567</t>
+          <t>14692</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>17885</t>
+          <t>7219</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10996</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>28172</t>
+          <t>14612</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>52740</t>
+          <t>14603</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>39214</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>68139</t>
+          <t>25425</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -3103,112 +3103,112 @@
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>vacunapreferencia</t>
+          <t>Otras personas</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>90800</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>73364</t>
+          <t>876</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>111372</t>
+          <t>8839</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>85822</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>69680</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>105793</t>
+          <t>10786</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>176622</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>152147</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>207189</t>
+          <t>15682</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -3216,112 +3216,112 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>medicootras</t>
+          <t>La empresa/centro de estudios</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>7384</t>
+          <t>34855</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2979</t>
+          <t>24584</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14692</t>
+          <t>48567</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>7219</t>
+          <t>17885</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14612</t>
+          <t>28172</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>52</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>14603</t>
+          <t>52740</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8863</t>
+          <t>39214</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>25425</t>
+          <t>68139</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -3329,112 +3329,112 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>otros</t>
+          <t>Por voluntad propia</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>90800</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>73364</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8839</t>
+          <t>111372</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>85822</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>69680</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10786</t>
+          <t>105793</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>167</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>176622</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3725</t>
+          <t>152147</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>15682</t>
+          <t>207189</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>medicoedad</t>
+          <t>El médico, por la edad</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>medicoenfermedad</t>
+          <t>El médico, por enfermedades</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -3903,112 +3903,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>vacunaempresa</t>
+          <t>El médico, por otras razones</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>11699</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6543</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13022</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>11348</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5634</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>20078</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -4016,112 +4016,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>vacunapreferencia</t>
+          <t>Otras personas</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31963</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44647</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34576</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24027</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46187</t>
+          <t>6722</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>66539</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50727</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83483</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -4129,112 +4129,112 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>medicootras</t>
+          <t>La empresa/centro de estudios</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11699</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2263</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13022</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>11348</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5634</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20078</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -4242,112 +4242,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>otros</t>
+          <t>Por voluntad propia</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31963</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21419</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>44647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>34576</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24027</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>46187</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>64</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>66539</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50727</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>83483</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>medicoedad</t>
+          <t>El médico, por la edad</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -4472,7 +4472,7 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>medicoenfermedad</t>
+          <t>El médico, por enfermedades</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -4585,112 +4585,112 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>vacunaempresa</t>
+          <t>El médico, por otras razones</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27106</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16685</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40186</t>
+          <t>19384</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18352</t>
+          <t>15095</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11094</t>
+          <t>8119</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29109</t>
+          <t>24613</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>45458</t>
+          <t>25396</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>31354</t>
+          <t>15906</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>60519</t>
+          <t>37759</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -4698,112 +4698,112 @@
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>vacunapreferencia</t>
+          <t>Otras personas</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>59656</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44284</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75536</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26595</t>
+          <t>4217</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18439</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40699</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>86251</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69341</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106222</t>
+          <t>12244</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -4811,112 +4811,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>medicootras</t>
+          <t>La empresa/centro de estudios</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>27106</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>16685</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19384</t>
+          <t>40186</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>15095</t>
+          <t>18352</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8119</t>
+          <t>11094</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24613</t>
+          <t>29109</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>41</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>25396</t>
+          <t>45458</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15906</t>
+          <t>31354</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37759</t>
+          <t>60519</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -4924,112 +4924,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>otros</t>
+          <t>Por voluntad propia</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>59656</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44284</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>75536</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>26595</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>18439</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>40699</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>81</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>86251</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>69341</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>12244</t>
+          <t>106222</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>medicoedad</t>
+          <t>El médico, por la edad</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -5154,7 +5154,7 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>medicoenfermedad</t>
+          <t>El médico, por enfermedades</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -5267,112 +5267,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>vacunaempresa</t>
+          <t>El médico, por otras razones</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17678</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10786</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28833</t>
+          <t>11841</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>995</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23079</t>
+          <t>11404</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>30150</t>
+          <t>6705</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20568</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>46491</t>
+          <t>15650</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -5380,112 +5380,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>vacunapreferencia</t>
+          <t>Otras personas</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12769</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21784</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7085</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2977</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15350</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>19854</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11986</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32781</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5493,112 +5493,112 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>medicootras</t>
+          <t>La empresa/centro de estudios</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>17678</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10786</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11841</t>
+          <t>28833</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11404</t>
+          <t>23079</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>6705</t>
+          <t>30150</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>20568</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15650</t>
+          <t>46491</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -5606,112 +5606,112 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>otros</t>
+          <t>Por voluntad propia</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12769</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6942</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21784</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7085</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15350</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19854</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11986</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>32781</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>medicoedad</t>
+          <t>El médico, por la edad</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>medicoenfermedad</t>
+          <t>El médico, por enfermedades</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -5949,112 +5949,112 @@
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>vacunaempresa</t>
+          <t>El médico, por otras razones</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>46660</t>
+          <t>17096</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>32875</t>
+          <t>9812</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>63554</t>
+          <t>27024</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>30824</t>
+          <t>26353</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21177</t>
+          <t>17284</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>47275</t>
+          <t>39354</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>39</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>77484</t>
+          <t>43449</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>59470</t>
+          <t>29072</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>98105</t>
+          <t>58383</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -6062,112 +6062,112 @@
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>vacunapreferencia</t>
+          <t>Otras personas</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>104389</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>85813</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>126463</t>
+          <t>6737</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>68256</t>
+          <t>5390</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53610</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>86513</t>
+          <t>12038</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>172644</t>
+          <t>7318</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>149151</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>200712</t>
+          <t>14358</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -6175,112 +6175,112 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>medicootras</t>
+          <t>La empresa/centro de estudios</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>17096</t>
+          <t>46660</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9812</t>
+          <t>32875</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27024</t>
+          <t>63554</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>26353</t>
+          <t>30824</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17284</t>
+          <t>21177</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>39354</t>
+          <t>47275</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>77484</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>59470</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>98105</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>1,11%</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>43449</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>29072</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>58383</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -6288,112 +6288,112 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>otros</t>
+          <t>Por voluntad propia</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>104389</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>85813</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6737</t>
+          <t>126463</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5390</t>
+          <t>68256</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>53610</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>12038</t>
+          <t>86513</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>163</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7318</t>
+          <t>172644</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>149151</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>14358</t>
+          <t>200712</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>medicoedad</t>
+          <t>El médico, por la edad</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -6749,7 +6749,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>medicoenfermedad</t>
+          <t>El médico, por enfermedades</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -6862,112 +6862,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>vacunaempresa</t>
+          <t>El médico, por otras razones</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>972</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6028</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13034</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>9980</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>18841</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -6975,112 +6975,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>vacunapreferencia</t>
+          <t>Otras personas</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22083</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14752</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32351</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25870</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15453</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37228</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>47952</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34731</t>
+          <t>967</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63239</t>
+          <t>9136</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -7088,112 +7088,112 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>medicootras</t>
+          <t>La empresa/centro de estudios</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6028</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13034</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>9980</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18841</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -7201,112 +7201,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>otros</t>
+          <t>Por voluntad propia</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>22083</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14752</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>32351</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>25870</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15453</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>37228</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>47</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>47952</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>34731</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>63239</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -7318,7 +7318,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>medicoedad</t>
+          <t>El médico, por la edad</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -7431,7 +7431,7 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>medicoenfermedad</t>
+          <t>El médico, por enfermedades</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -7544,112 +7544,112 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>vacunaempresa</t>
+          <t>El médico, por otras razones</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8826</t>
+          <t>12750</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3897</t>
+          <t>6400</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17360</t>
+          <t>21142</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9503</t>
+          <t>11164</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17682</t>
+          <t>19481</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>18329</t>
+          <t>23915</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11156</t>
+          <t>15223</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28824</t>
+          <t>36552</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -7657,112 +7657,112 @@
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>vacunapreferencia</t>
+          <t>Otras personas</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24089</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14930</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36935</t>
+          <t>12939</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26284</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17376</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38861</t>
+          <t>13247</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>50372</t>
+          <t>12523</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37322</t>
+          <t>6346</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66439</t>
+          <t>20817</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -7770,112 +7770,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>medicootras</t>
+          <t>La empresa/centro de estudios</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12750</t>
+          <t>8826</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21142</t>
+          <t>17360</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11164</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19481</t>
+          <t>17682</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>23915</t>
+          <t>18329</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15223</t>
+          <t>11156</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36552</t>
+          <t>28824</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -7883,112 +7883,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>otros</t>
+          <t>Por voluntad propia</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>24089</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>14930</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12939</t>
+          <t>36935</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6459</t>
+          <t>26284</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>17376</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13247</t>
+          <t>38861</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>12523</t>
+          <t>50372</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6346</t>
+          <t>37322</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>20817</t>
+          <t>66439</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>medicoedad</t>
+          <t>El médico, por la edad</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -8113,7 +8113,7 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>medicoenfermedad</t>
+          <t>El médico, por enfermedades</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -8226,112 +8226,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>vacunaempresa</t>
+          <t>El médico, por otras razones</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>903</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11657</t>
+          <t>12011</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9593</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4554</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17458</t>
+          <t>13015</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>9176</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>24710</t>
+          <t>18994</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -8339,112 +8339,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>vacunapreferencia</t>
+          <t>Otras personas</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8576</t>
+          <t>5455</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4072</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16891</t>
+          <t>13290</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11631</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>880</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20405</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>20207</t>
+          <t>8671</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12949</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31775</t>
+          <t>18307</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -8452,112 +8452,112 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>medicootras</t>
+          <t>La empresa/centro de estudios</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12011</t>
+          <t>11657</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5490</t>
+          <t>9593</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>4554</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13015</t>
+          <t>17458</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>9176</t>
+          <t>14414</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18994</t>
+          <t>24710</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -8565,112 +8565,112 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>otros</t>
+          <t>Por voluntad propia</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5455</t>
+          <t>8576</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1577</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13290</t>
+          <t>16891</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>11631</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9551</t>
+          <t>20405</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>20207</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>12949</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>18307</t>
+          <t>31775</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>medicoedad</t>
+          <t>El médico, por la edad</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -8795,7 +8795,7 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>medicoenfermedad</t>
+          <t>El médico, por enfermedades</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -8908,112 +8908,112 @@
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>vacunaempresa</t>
+          <t>El médico, por otras razones</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>14697</t>
+          <t>20388</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8188</t>
+          <t>12776</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25004</t>
+          <t>32660</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>19095</t>
+          <t>22682</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11519</t>
+          <t>14571</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29056</t>
+          <t>34511</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>41</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>33792</t>
+          <t>43071</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>23946</t>
+          <t>31490</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>49313</t>
+          <t>58389</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -9021,112 +9021,112 @@
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>vacunapreferencia</t>
+          <t>Otras personas</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>54747</t>
+          <t>12579</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>40334</t>
+          <t>6719</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>71761</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>63785</t>
+          <t>11689</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>50723</t>
+          <t>5576</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>83115</t>
+          <t>19860</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>118532</t>
+          <t>24268</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>98753</t>
+          <t>15420</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>142588</t>
+          <t>37771</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -9134,112 +9134,112 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>medicootras</t>
+          <t>La empresa/centro de estudios</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>20388</t>
+          <t>14697</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12776</t>
+          <t>8188</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>32660</t>
+          <t>25004</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>22682</t>
+          <t>19095</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14571</t>
+          <t>11519</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>34511</t>
+          <t>29056</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>31</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>43071</t>
+          <t>33792</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>31490</t>
+          <t>23946</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>58389</t>
+          <t>49313</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -9247,112 +9247,112 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>otros</t>
+          <t>Por voluntad propia</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>12579</t>
+          <t>54747</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6719</t>
+          <t>40334</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>71761</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>11689</t>
+          <t>63785</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>5576</t>
+          <t>50723</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>19860</t>
+          <t>83115</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>112</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>24268</t>
+          <t>118532</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>15420</t>
+          <t>98753</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>37771</t>
+          <t>142588</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>medicoedad</t>
+          <t>El médico, por la edad</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -9708,7 +9708,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>medicoenfermedad</t>
+          <t>El médico, por enfermedades</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -9821,112 +9821,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>vacunaempresa</t>
+          <t>El médico, por otras razones</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>7601</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>14407</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
+          <t>7376</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>3746</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1344</t>
-        </is>
-      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8794</t>
+          <t>12341</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>14977</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>9255</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>23349</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
           <t>1,07%</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>6054</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>2605</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>13163</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -9934,112 +9934,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>vacunapreferencia</t>
+          <t>Otras personas</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41967</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31888</t>
+          <t>911</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55475</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>59158</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48138</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70820</t>
+          <t>9348</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>101125</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86699</t>
+          <t>4208</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>118352</t>
+          <t>14515</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -10047,112 +10047,112 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>medicootras</t>
+          <t>La empresa/centro de estudios</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9209</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>3746</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1344</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>8794</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7601</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3291</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14407</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>7376</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>3746</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>12341</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>14977</t>
+          <t>6054</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9255</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23349</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -10160,112 +10160,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>otros</t>
+          <t>Por voluntad propia</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>41967</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>31888</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9684</t>
+          <t>55475</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>101</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>59158</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>48138</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>70820</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>150</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>101125</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4208</t>
+          <t>86699</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14515</t>
+          <t>118352</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -10277,7 +10277,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>medicoedad</t>
+          <t>El médico, por la edad</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10390,7 +10390,7 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>medicoenfermedad</t>
+          <t>El médico, por enfermedades</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10503,112 +10503,112 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>vacunaempresa</t>
+          <t>El médico, por otras razones</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>54517</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40875</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70590</t>
+          <t>22664</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>66009</t>
+          <t>30719</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52469</t>
+          <t>21821</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>81159</t>
+          <t>42153</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>51</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>120526</t>
+          <t>42012</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>99788</t>
+          <t>30924</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>141184</t>
+          <t>56874</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -10616,112 +10616,112 @@
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>vacunapreferencia</t>
+          <t>Otras personas</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>173302</t>
+          <t>16364</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>147146</t>
+          <t>9061</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>201326</t>
+          <t>28000</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>168672</t>
+          <t>25393</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>146921</t>
+          <t>16260</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>192596</t>
+          <t>37570</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>42</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>341974</t>
+          <t>41757</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>309269</t>
+          <t>30180</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>379306</t>
+          <t>58964</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -10729,112 +10729,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>medicootras</t>
+          <t>La empresa/centro de estudios</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11293</t>
+          <t>54517</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5571</t>
+          <t>40875</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22664</t>
+          <t>70590</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>30719</t>
+          <t>66009</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21821</t>
+          <t>52469</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42153</t>
+          <t>81159</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>138</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>42012</t>
+          <t>120526</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30924</t>
+          <t>99788</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56874</t>
+          <t>141184</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -10842,112 +10842,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>otros</t>
+          <t>Por voluntad propia</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>170</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16364</t>
+          <t>173302</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9061</t>
+          <t>147146</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28000</t>
+          <t>201326</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>243</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25393</t>
+          <t>168672</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16260</t>
+          <t>146921</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>37570</t>
+          <t>192596</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>413</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>41757</t>
+          <t>341974</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>30180</t>
+          <t>309269</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>58964</t>
+          <t>379306</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -10959,7 +10959,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>medicoedad</t>
+          <t>El médico, por la edad</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -11072,7 +11072,7 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>medicoenfermedad</t>
+          <t>El médico, por enfermedades</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -11185,112 +11185,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>vacunaempresa</t>
+          <t>El médico, por otras razones</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>37982</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27541</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51246</t>
+          <t>9339</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>47647</t>
+          <t>11186</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37284</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63027</t>
+          <t>18798</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>85629</t>
+          <t>15335</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>68787</t>
+          <t>9057</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>102620</t>
+          <t>23355</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -11298,112 +11298,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>vacunapreferencia</t>
+          <t>Otras personas</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>59167</t>
+          <t>13279</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45018</t>
+          <t>6935</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76389</t>
+          <t>25967</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>64919</t>
+          <t>8865</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52877</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78672</t>
+          <t>15988</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>24</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>124086</t>
+          <t>22144</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>104983</t>
+          <t>14194</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>145725</t>
+          <t>34189</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -11411,112 +11411,112 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>medicootras</t>
+          <t>La empresa/centro de estudios</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>37982</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>27541</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9339</t>
+          <t>51246</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11186</t>
+          <t>47647</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>37284</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18798</t>
+          <t>63027</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>98</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>15335</t>
+          <t>85629</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9057</t>
+          <t>68787</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23355</t>
+          <t>102620</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -11524,112 +11524,112 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>otros</t>
+          <t>Por voluntad propia</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13279</t>
+          <t>59167</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6935</t>
+          <t>45018</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25967</t>
+          <t>76389</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8865</t>
+          <t>64919</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>52877</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15988</t>
+          <t>78672</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>157</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>22144</t>
+          <t>124086</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14194</t>
+          <t>104983</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>34189</t>
+          <t>145725</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -11641,7 +11641,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>medicoedad</t>
+          <t>El médico, por la edad</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -11754,7 +11754,7 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>medicoenfermedad</t>
+          <t>El médico, por enfermedades</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -11867,112 +11867,112 @@
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>vacunaempresa</t>
+          <t>El médico, por otras razones</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>23043</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>14454</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>34720</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>49281</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>37814</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>61735</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>94807</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>76225</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>116610</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>117402</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>98433</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>137782</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>212209</t>
+          <t>72324</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>186413</t>
+          <t>57661</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>241161</t>
+          <t>90050</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -11980,112 +11980,112 @@
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>vacunapreferencia</t>
+          <t>Otras personas</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>274436</t>
+          <t>32872</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>240985</t>
+          <t>21831</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>309044</t>
+          <t>47772</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>292749</t>
+          <t>39162</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>264642</t>
+          <t>28162</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>321636</t>
+          <t>53975</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>77</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>567185</t>
+          <t>72034</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>523338</t>
+          <t>55604</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>610179</t>
+          <t>92587</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -12093,112 +12093,112 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>medicootras</t>
+          <t>La empresa/centro de estudios</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>23043</t>
+          <t>94807</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14454</t>
+          <t>76225</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>34720</t>
+          <t>116610</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>154</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>49281</t>
+          <t>117402</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>37814</t>
+          <t>98433</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>61735</t>
+          <t>137782</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>243</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>72324</t>
+          <t>212209</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>57661</t>
+          <t>186413</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>90050</t>
+          <t>241161</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -12206,112 +12206,112 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>otros</t>
+          <t>Por voluntad propia</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>284</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>32872</t>
+          <t>274436</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>21831</t>
+          <t>240985</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>47772</t>
+          <t>309044</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>436</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>39162</t>
+          <t>292749</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>28162</t>
+          <t>264642</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>53975</t>
+          <t>321636</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>720</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>72034</t>
+          <t>567185</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>55604</t>
+          <t>523338</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>92587</t>
+          <t>610179</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
